--- a/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-prescription-item.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="198">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,6 +543,9 @@
   </si>
   <si>
     <t>Type de substitution</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis (2.16.840.1.113883.1.11.16621)</t>
@@ -3839,13 +3842,13 @@
         <v>73</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -3880,10 +3883,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3909,10 +3912,10 @@
         <v>143</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3963,7 +3966,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -3980,10 +3983,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4006,13 +4009,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4063,7 +4066,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4080,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4109,10 +4112,10 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4163,7 +4166,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4180,10 +4183,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4209,10 +4212,10 @@
         <v>80</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4263,7 +4266,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4280,10 +4283,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4306,13 +4309,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4363,7 +4366,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4380,10 +4383,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4409,10 +4412,10 @@
         <v>143</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4463,7 +4466,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -4480,10 +4483,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4506,13 +4509,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4563,7 +4566,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -4580,10 +4583,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4606,13 +4609,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4663,7 +4666,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4680,10 +4683,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4706,13 +4709,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4763,7 +4766,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4780,10 +4783,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4806,13 +4809,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4863,7 +4866,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4880,10 +4883,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4906,13 +4909,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4963,7 +4966,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
